--- a/Hoadon/HD2026/HDRa/4/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDRa/4/3502550210_HDDienTuMayTinhTien.xlsx
@@ -6592,6 +6592,3291 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>95.0</v>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H101" s="7"/>
+      <c r="I101" s="6"/>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>122/29 Lý Tự Trọng Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>093083010956</t>
+        </is>
+      </c>
+      <c r="L101" s="13" t="n">
+        <v>3020365.0</v>
+      </c>
+      <c r="M101" s="13" t="n">
+        <v>241630.0</v>
+      </c>
+      <c r="N101" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O101" s="13" t="n">
+        <v>3261995.0</v>
+      </c>
+      <c r="P101" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q101" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>96.0</v>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H102" s="7"/>
+      <c r="I102" s="6"/>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K102" s="6"/>
+      <c r="L102" s="13" t="n">
+        <v>1.774997E7</v>
+      </c>
+      <c r="M102" s="13" t="n">
+        <v>1726664.0</v>
+      </c>
+      <c r="N102" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O102" s="13" t="n">
+        <v>1.9476634E7</v>
+      </c>
+      <c r="P102" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q102" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n">
+        <v>97.0</v>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H103" s="7"/>
+      <c r="I103" s="6"/>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>1507/2 A Đường 30/4 Phường Phước Thắng Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>077096003835</t>
+        </is>
+      </c>
+      <c r="L103" s="13" t="n">
+        <v>3826601.0</v>
+      </c>
+      <c r="M103" s="13" t="n">
+        <v>313401.0</v>
+      </c>
+      <c r="N103" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O103" s="13" t="n">
+        <v>4140002.0</v>
+      </c>
+      <c r="P103" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q103" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>98.0</v>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H104" s="7"/>
+      <c r="I104" s="6"/>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K104" s="6"/>
+      <c r="L104" s="13" t="n">
+        <v>5839330.0</v>
+      </c>
+      <c r="M104" s="13" t="n">
+        <v>500783.0</v>
+      </c>
+      <c r="N104" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O104" s="13" t="n">
+        <v>6340113.0</v>
+      </c>
+      <c r="P104" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q104" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>99.0</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H105" s="7"/>
+      <c r="I105" s="6"/>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K105" s="6"/>
+      <c r="L105" s="13" t="n">
+        <v>7479475.0</v>
+      </c>
+      <c r="M105" s="13" t="n">
+        <v>708088.0</v>
+      </c>
+      <c r="N105" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O105" s="13" t="n">
+        <v>8187563.0</v>
+      </c>
+      <c r="P105" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q105" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H106" s="7"/>
+      <c r="I106" s="6"/>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K106" s="6"/>
+      <c r="L106" s="13" t="n">
+        <v>1.77272E7</v>
+      </c>
+      <c r="M106" s="13" t="n">
+        <v>1772720.0</v>
+      </c>
+      <c r="N106" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O106" s="13" t="n">
+        <v>1.949992E7</v>
+      </c>
+      <c r="P106" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q106" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n">
+        <v>101.0</v>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>811</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H107" s="7"/>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>LÊ MINH THIỆN</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>40 Đường Vi Ba Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>077093000458</t>
+        </is>
+      </c>
+      <c r="L107" s="13" t="n">
+        <v>3176437.0</v>
+      </c>
+      <c r="M107" s="13" t="n">
+        <v>264587.0</v>
+      </c>
+      <c r="N107" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O107" s="13" t="n">
+        <v>3441024.0</v>
+      </c>
+      <c r="P107" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q107" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="n">
+        <v>102.0</v>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H108" s="7"/>
+      <c r="I108" s="6"/>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K108" s="6"/>
+      <c r="L108" s="13" t="n">
+        <v>5924364.0</v>
+      </c>
+      <c r="M108" s="13" t="n">
+        <v>535030.0</v>
+      </c>
+      <c r="N108" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O108" s="13" t="n">
+        <v>6459394.0</v>
+      </c>
+      <c r="P108" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q108" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n">
+        <v>103.0</v>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H109" s="7"/>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>HỒ PHƯỚC KIM BẢO</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>100 Nguyễn Hữu Cảnh Phường Tam Thắng Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K109" s="6"/>
+      <c r="L109" s="13" t="n">
+        <v>2718466.0</v>
+      </c>
+      <c r="M109" s="13" t="n">
+        <v>217478.0</v>
+      </c>
+      <c r="N109" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O109" s="13" t="n">
+        <v>2935944.0</v>
+      </c>
+      <c r="P109" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q109" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="n">
+        <v>104.0</v>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H110" s="7"/>
+      <c r="I110" s="6"/>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K110" s="6"/>
+      <c r="L110" s="13" t="n">
+        <v>5532410.0</v>
+      </c>
+      <c r="M110" s="13" t="n">
+        <v>442593.0</v>
+      </c>
+      <c r="N110" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O110" s="13" t="n">
+        <v>5975003.0</v>
+      </c>
+      <c r="P110" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q110" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>105.0</v>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H111" s="7"/>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J111" s="6"/>
+      <c r="K111" s="6"/>
+      <c r="L111" s="13" t="n">
+        <v>5359913.0</v>
+      </c>
+      <c r="M111" s="13" t="n">
+        <v>522732.0</v>
+      </c>
+      <c r="N111" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O111" s="13" t="n">
+        <v>5882645.0</v>
+      </c>
+      <c r="P111" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q111" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n">
+        <v>106.0</v>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H112" s="7"/>
+      <c r="I112" s="6"/>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K112" s="6"/>
+      <c r="L112" s="13" t="n">
+        <v>5.0909E7</v>
+      </c>
+      <c r="M112" s="13" t="n">
+        <v>5090900.0</v>
+      </c>
+      <c r="N112" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O112" s="13" t="n">
+        <v>5.59999E7</v>
+      </c>
+      <c r="P112" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q112" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="n">
+        <v>107.0</v>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H113" s="7"/>
+      <c r="I113" s="6"/>
+      <c r="J113" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K113" s="6"/>
+      <c r="L113" s="13" t="n">
+        <v>1.161107E7</v>
+      </c>
+      <c r="M113" s="13" t="n">
+        <v>1128885.0</v>
+      </c>
+      <c r="N113" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O113" s="13" t="n">
+        <v>1.2739955E7</v>
+      </c>
+      <c r="P113" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q113" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="n">
+        <v>108.0</v>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H114" s="7"/>
+      <c r="I114" s="6"/>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K114" s="6"/>
+      <c r="L114" s="13" t="n">
+        <v>9949470.0</v>
+      </c>
+      <c r="M114" s="13" t="n">
+        <v>962725.0</v>
+      </c>
+      <c r="N114" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O114" s="13" t="n">
+        <v>1.0912195E7</v>
+      </c>
+      <c r="P114" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q114" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n">
+        <v>109.0</v>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H115" s="7" t="inlineStr">
+        <is>
+          <t>8498858337</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>LẠI THỊ ÁNH HỒNG</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>118 Nguyễn Văn Trỗi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh .</t>
+        </is>
+      </c>
+      <c r="K115" s="6"/>
+      <c r="L115" s="13" t="n">
+        <v>3797484.0</v>
+      </c>
+      <c r="M115" s="13" t="n">
+        <v>312526.0</v>
+      </c>
+      <c r="N115" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O115" s="13" t="n">
+        <v>4110010.0</v>
+      </c>
+      <c r="P115" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q115" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="n">
+        <v>110.0</v>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H116" s="7"/>
+      <c r="I116" s="6"/>
+      <c r="J116" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K116" s="6"/>
+      <c r="L116" s="13" t="n">
+        <v>5166808.0</v>
+      </c>
+      <c r="M116" s="13" t="n">
+        <v>433163.0</v>
+      </c>
+      <c r="N116" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O116" s="13" t="n">
+        <v>5599971.0</v>
+      </c>
+      <c r="P116" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q116" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="n">
+        <v>111.0</v>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H117" s="7"/>
+      <c r="I117" s="6"/>
+      <c r="J117" s="6" t="inlineStr">
+        <is>
+          <t>1507/2 A Đường 30/4 Phường Phước Thắng Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K117" s="6" t="inlineStr">
+        <is>
+          <t>077096003835</t>
+        </is>
+      </c>
+      <c r="L117" s="13" t="n">
+        <v>6707502.0</v>
+      </c>
+      <c r="M117" s="13" t="n">
+        <v>647509.0</v>
+      </c>
+      <c r="N117" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O117" s="13" t="n">
+        <v>7355011.0</v>
+      </c>
+      <c r="P117" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q117" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="n">
+        <v>112.0</v>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H118" s="7"/>
+      <c r="I118" s="6"/>
+      <c r="J118" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K118" s="6"/>
+      <c r="L118" s="13" t="n">
+        <v>8917550.0</v>
+      </c>
+      <c r="M118" s="13" t="n">
+        <v>843422.0</v>
+      </c>
+      <c r="N118" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O118" s="13" t="n">
+        <v>9760972.0</v>
+      </c>
+      <c r="P118" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q118" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="n">
+        <v>113.0</v>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H119" s="7"/>
+      <c r="I119" s="6"/>
+      <c r="J119" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K119" s="6"/>
+      <c r="L119" s="13" t="n">
+        <v>5408325.0</v>
+      </c>
+      <c r="M119" s="13" t="n">
+        <v>432666.0</v>
+      </c>
+      <c r="N119" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O119" s="13" t="n">
+        <v>5840991.0</v>
+      </c>
+      <c r="P119" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q119" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="n">
+        <v>114.0</v>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H120" s="7"/>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>LÊ QUỐC TUẤN</t>
+        </is>
+      </c>
+      <c r="J120" s="6" t="inlineStr">
+        <is>
+          <t>195/6 Hoàng Văn Thụ, Phường Tam Thắng Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K120" s="6"/>
+      <c r="L120" s="13" t="n">
+        <v>3908439.0</v>
+      </c>
+      <c r="M120" s="13" t="n">
+        <v>361122.0</v>
+      </c>
+      <c r="N120" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O120" s="13" t="n">
+        <v>4269561.0</v>
+      </c>
+      <c r="P120" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q120" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="n">
+        <v>115.0</v>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H121" s="7"/>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>LÊ HOÀNG LONG</t>
+        </is>
+      </c>
+      <c r="J121" s="6" t="inlineStr">
+        <is>
+          <t>293 Thống Nhất, Phường Tam Thắng, Thành Phố Hồ Chí Minh.</t>
+        </is>
+      </c>
+      <c r="K121" s="6" t="inlineStr">
+        <is>
+          <t>027089001129</t>
+        </is>
+      </c>
+      <c r="L121" s="13" t="n">
+        <v>4984864.0</v>
+      </c>
+      <c r="M121" s="13" t="n">
+        <v>435154.0</v>
+      </c>
+      <c r="N121" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O121" s="13" t="n">
+        <v>5420018.0</v>
+      </c>
+      <c r="P121" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q121" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="n">
+        <v>116.0</v>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H122" s="7"/>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J122" s="6"/>
+      <c r="K122" s="6"/>
+      <c r="L122" s="13" t="n">
+        <v>6971696.0</v>
+      </c>
+      <c r="M122" s="13" t="n">
+        <v>664949.0</v>
+      </c>
+      <c r="N122" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O122" s="13" t="n">
+        <v>7636645.0</v>
+      </c>
+      <c r="P122" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q122" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="n">
+        <v>117.0</v>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H123" s="7"/>
+      <c r="I123" s="6"/>
+      <c r="J123" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K123" s="6"/>
+      <c r="L123" s="13" t="n">
+        <v>8372790.0</v>
+      </c>
+      <c r="M123" s="13" t="n">
+        <v>837279.0</v>
+      </c>
+      <c r="N123" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O123" s="13" t="n">
+        <v>9210069.0</v>
+      </c>
+      <c r="P123" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q123" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="n">
+        <v>118.0</v>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H124" s="7"/>
+      <c r="I124" s="6"/>
+      <c r="J124" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K124" s="6"/>
+      <c r="L124" s="13" t="n">
+        <v>3808326.0</v>
+      </c>
+      <c r="M124" s="13" t="n">
+        <v>304666.0</v>
+      </c>
+      <c r="N124" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O124" s="13" t="n">
+        <v>4112992.0</v>
+      </c>
+      <c r="P124" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q124" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="n">
+        <v>119.0</v>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H125" s="7"/>
+      <c r="I125" s="6"/>
+      <c r="J125" s="6" t="inlineStr">
+        <is>
+          <t>57/8 A Nguyễn Hữu  Cảnh, Phường Rạch Dừa Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K125" s="6" t="inlineStr">
+        <is>
+          <t>093185007857</t>
+        </is>
+      </c>
+      <c r="L125" s="13" t="n">
+        <v>3467585.0</v>
+      </c>
+      <c r="M125" s="13" t="n">
+        <v>277407.0</v>
+      </c>
+      <c r="N125" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O125" s="13" t="n">
+        <v>3744992.0</v>
+      </c>
+      <c r="P125" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q125" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H126" s="7"/>
+      <c r="I126" s="6"/>
+      <c r="J126" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K126" s="6"/>
+      <c r="L126" s="13" t="n">
+        <v>8277750.0</v>
+      </c>
+      <c r="M126" s="13" t="n">
+        <v>782220.0</v>
+      </c>
+      <c r="N126" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O126" s="13" t="n">
+        <v>9059970.0</v>
+      </c>
+      <c r="P126" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q126" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="n">
+        <v>121.0</v>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t>060170001301</t>
+        </is>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH NGUYỄN THỊ THÙY LINH-13/7/1970</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="inlineStr">
+        <is>
+          <t>86/11 Nguyễn An Ninh, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K127" s="6"/>
+      <c r="L127" s="13" t="n">
+        <v>2697999.0</v>
+      </c>
+      <c r="M127" s="13" t="n">
+        <v>258387.0</v>
+      </c>
+      <c r="N127" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O127" s="13" t="n">
+        <v>2956386.0</v>
+      </c>
+      <c r="P127" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q127" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="n">
+        <v>122.0</v>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H128" s="7"/>
+      <c r="I128" s="6"/>
+      <c r="J128" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K128" s="6"/>
+      <c r="L128" s="13" t="n">
+        <v>1.574072E7</v>
+      </c>
+      <c r="M128" s="13" t="n">
+        <v>1367407.0</v>
+      </c>
+      <c r="N128" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O128" s="13" t="n">
+        <v>1.7108127E7</v>
+      </c>
+      <c r="P128" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q128" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="n">
+        <v>123.0</v>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H129" s="7"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K129" s="6"/>
+      <c r="L129" s="13" t="n">
+        <v>1.498182E7</v>
+      </c>
+      <c r="M129" s="13" t="n">
+        <v>1498182.0</v>
+      </c>
+      <c r="N129" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O129" s="13" t="n">
+        <v>1.6480002E7</v>
+      </c>
+      <c r="P129" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q129" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>124.0</v>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>834</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H130" s="7"/>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>LÊ MINH THIỆN</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="inlineStr">
+        <is>
+          <t>40 Đường Vi Ba Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K130" s="6" t="inlineStr">
+        <is>
+          <t>077093000458</t>
+        </is>
+      </c>
+      <c r="L130" s="13" t="n">
+        <v>3398255.0</v>
+      </c>
+      <c r="M130" s="13" t="n">
+        <v>271861.0</v>
+      </c>
+      <c r="N130" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O130" s="13" t="n">
+        <v>3670116.0</v>
+      </c>
+      <c r="P130" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q130" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="n">
+        <v>125.0</v>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H131" s="7"/>
+      <c r="I131" s="6"/>
+      <c r="J131" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K131" s="6"/>
+      <c r="L131" s="13" t="n">
+        <v>4739808.0</v>
+      </c>
+      <c r="M131" s="13" t="n">
+        <v>416222.0</v>
+      </c>
+      <c r="N131" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O131" s="13" t="n">
+        <v>5156030.0</v>
+      </c>
+      <c r="P131" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q131" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>126.0</v>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>077088009229</t>
+        </is>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH TÂM NGUYỄN (DƯƠNG THẾ HUY)</t>
+        </is>
+      </c>
+      <c r="J132" s="6" t="inlineStr">
+        <is>
+          <t>04 đường Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K132" s="6"/>
+      <c r="L132" s="13" t="n">
+        <v>3.63934E7</v>
+      </c>
+      <c r="M132" s="13" t="n">
+        <v>2911472.0</v>
+      </c>
+      <c r="N132" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O132" s="13" t="n">
+        <v>3.9304872E7</v>
+      </c>
+      <c r="P132" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q132" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="n">
+        <v>127.0</v>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H133" s="7"/>
+      <c r="I133" s="6"/>
+      <c r="J133" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K133" s="6"/>
+      <c r="L133" s="13" t="n">
+        <v>3687407.0</v>
+      </c>
+      <c r="M133" s="13" t="n">
+        <v>320540.0</v>
+      </c>
+      <c r="N133" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O133" s="13" t="n">
+        <v>4007947.0</v>
+      </c>
+      <c r="P133" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q133" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="n">
+        <v>128.0</v>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H134" s="7"/>
+      <c r="I134" s="6"/>
+      <c r="J134" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K134" s="6"/>
+      <c r="L134" s="13" t="n">
+        <v>7578025.0</v>
+      </c>
+      <c r="M134" s="13" t="n">
+        <v>630970.0</v>
+      </c>
+      <c r="N134" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O134" s="13" t="n">
+        <v>8208995.0</v>
+      </c>
+      <c r="P134" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q134" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="n">
+        <v>129.0</v>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H135" s="7"/>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>LÊ QUỐC TUẤN</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="inlineStr">
+        <is>
+          <t>195/6 Hoàng Văn Thụ, Phường Tam Thắng Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K135" s="6"/>
+      <c r="L135" s="13" t="n">
+        <v>7588032.0</v>
+      </c>
+      <c r="M135" s="13" t="n">
+        <v>721952.0</v>
+      </c>
+      <c r="N135" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O135" s="13" t="n">
+        <v>8309984.0</v>
+      </c>
+      <c r="P135" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q135" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="n">
+        <v>130.0</v>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H136" s="7"/>
+      <c r="I136" s="6"/>
+      <c r="J136" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K136" s="6"/>
+      <c r="L136" s="13" t="n">
+        <v>1.550757E7</v>
+      </c>
+      <c r="M136" s="13" t="n">
+        <v>1502424.0</v>
+      </c>
+      <c r="N136" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O136" s="13" t="n">
+        <v>1.7009994E7</v>
+      </c>
+      <c r="P136" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q136" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="n">
+        <v>131.0</v>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H137" s="7"/>
+      <c r="I137" s="6"/>
+      <c r="J137" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K137" s="6"/>
+      <c r="L137" s="13" t="n">
+        <v>8338435.0</v>
+      </c>
+      <c r="M137" s="13" t="n">
+        <v>823010.0</v>
+      </c>
+      <c r="N137" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O137" s="13" t="n">
+        <v>9161445.0</v>
+      </c>
+      <c r="P137" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q137" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H138" s="7"/>
+      <c r="I138" s="6"/>
+      <c r="J138" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K138" s="6"/>
+      <c r="L138" s="13" t="n">
+        <v>5891159.0</v>
+      </c>
+      <c r="M138" s="13" t="n">
+        <v>561838.0</v>
+      </c>
+      <c r="N138" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O138" s="13" t="n">
+        <v>6452997.0</v>
+      </c>
+      <c r="P138" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q138" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="n">
+        <v>133.0</v>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>843</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H139" s="7"/>
+      <c r="I139" s="6"/>
+      <c r="J139" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K139" s="6"/>
+      <c r="L139" s="13" t="n">
+        <v>1.4999822E7</v>
+      </c>
+      <c r="M139" s="13" t="n">
+        <v>1418168.0</v>
+      </c>
+      <c r="N139" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O139" s="13" t="n">
+        <v>1.641799E7</v>
+      </c>
+      <c r="P139" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q139" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="n">
+        <v>134.0</v>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H140" s="7"/>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J140" s="6"/>
+      <c r="K140" s="6"/>
+      <c r="L140" s="13" t="n">
+        <v>1.781818E7</v>
+      </c>
+      <c r="M140" s="13" t="n">
+        <v>1781818.0</v>
+      </c>
+      <c r="N140" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O140" s="13" t="n">
+        <v>1.9599998E7</v>
+      </c>
+      <c r="P140" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q140" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="n">
+        <v>135.0</v>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H141" s="7"/>
+      <c r="I141" s="6"/>
+      <c r="J141" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K141" s="6"/>
+      <c r="L141" s="13" t="n">
+        <v>4635209.0</v>
+      </c>
+      <c r="M141" s="13" t="n">
+        <v>393040.0</v>
+      </c>
+      <c r="N141" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O141" s="13" t="n">
+        <v>5028249.0</v>
+      </c>
+      <c r="P141" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q141" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="n">
+        <v>136.0</v>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H142" s="7"/>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J142" s="6"/>
+      <c r="K142" s="6"/>
+      <c r="L142" s="13" t="n">
+        <v>4037026.0</v>
+      </c>
+      <c r="M142" s="13" t="n">
+        <v>322963.0</v>
+      </c>
+      <c r="N142" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O142" s="13" t="n">
+        <v>4359989.0</v>
+      </c>
+      <c r="P142" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q142" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="n">
+        <v>137.0</v>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H143" s="7"/>
+      <c r="I143" s="6"/>
+      <c r="J143" s="6" t="inlineStr">
+        <is>
+          <t>57/8 A Nguyễn Hữu  Cảnh, Phường Rạch Dừa Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K143" s="6" t="inlineStr">
+        <is>
+          <t>093185007857</t>
+        </is>
+      </c>
+      <c r="L143" s="13" t="n">
+        <v>5053024.0</v>
+      </c>
+      <c r="M143" s="13" t="n">
+        <v>483359.0</v>
+      </c>
+      <c r="N143" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O143" s="13" t="n">
+        <v>5536383.0</v>
+      </c>
+      <c r="P143" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q143" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="n">
+        <v>138.0</v>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H144" s="7"/>
+      <c r="I144" s="6"/>
+      <c r="J144" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K144" s="6"/>
+      <c r="L144" s="13" t="n">
+        <v>2.018181E7</v>
+      </c>
+      <c r="M144" s="13" t="n">
+        <v>2018181.0</v>
+      </c>
+      <c r="N144" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O144" s="13" t="n">
+        <v>2.2199991E7</v>
+      </c>
+      <c r="P144" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q144" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="n">
+        <v>139.0</v>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H145" s="7"/>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>Trần Thanh Hưng</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="inlineStr">
+        <is>
+          <t>507 B đường 2/9, Phường Rạch Dừa Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>052090000956</t>
+        </is>
+      </c>
+      <c r="L145" s="13" t="n">
+        <v>3088918.0</v>
+      </c>
+      <c r="M145" s="13" t="n">
+        <v>305467.0</v>
+      </c>
+      <c r="N145" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O145" s="13" t="n">
+        <v>3394385.0</v>
+      </c>
+      <c r="P145" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q145" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="n">
+        <v>140.0</v>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H146" s="7"/>
+      <c r="I146" s="6"/>
+      <c r="J146" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K146" s="6"/>
+      <c r="L146" s="13" t="n">
+        <v>4434307.0</v>
+      </c>
+      <c r="M146" s="13" t="n">
+        <v>373263.0</v>
+      </c>
+      <c r="N146" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O146" s="13" t="n">
+        <v>4807570.0</v>
+      </c>
+      <c r="P146" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q146" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="n">
+        <v>141.0</v>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H147" s="7"/>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>LÊ QUỐC TUẤN</t>
+        </is>
+      </c>
+      <c r="J147" s="6" t="inlineStr">
+        <is>
+          <t>195/6 Hoàng Văn Thụ, Phường Tam Thắng Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K147" s="6"/>
+      <c r="L147" s="13" t="n">
+        <v>5710420.0</v>
+      </c>
+      <c r="M147" s="13" t="n">
+        <v>529560.0</v>
+      </c>
+      <c r="N147" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O147" s="13" t="n">
+        <v>6239980.0</v>
+      </c>
+      <c r="P147" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q147" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n">
+        <v>142.0</v>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H148" s="7" t="inlineStr">
+        <is>
+          <t>3502394603</t>
+        </is>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ PHẾ LIỆU ĐẠI MINH PHÁT</t>
+        </is>
+      </c>
+      <c r="J148" s="6" t="inlineStr">
+        <is>
+          <t>Số 9E đường Ven Biển, Phường Phước Thắng, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K148" s="6"/>
+      <c r="L148" s="13" t="n">
+        <v>4372170.0</v>
+      </c>
+      <c r="M148" s="13" t="n">
+        <v>349774.0</v>
+      </c>
+      <c r="N148" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O148" s="13" t="n">
+        <v>4721944.0</v>
+      </c>
+      <c r="P148" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q148" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="n">
+        <v>143.0</v>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H149" s="7"/>
+      <c r="I149" s="6"/>
+      <c r="J149" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K149" s="6"/>
+      <c r="L149" s="13" t="n">
+        <v>8477742.0</v>
+      </c>
+      <c r="M149" s="13" t="n">
+        <v>711552.0</v>
+      </c>
+      <c r="N149" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O149" s="13" t="n">
+        <v>9189294.0</v>
+      </c>
+      <c r="P149" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q149" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>

--- a/Hoadon/HD2026/HDRa/4/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDRa/4/3502550210_HDDienTuMayTinhTien.xlsx
@@ -9877,6 +9877,4534 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="4" t="n">
+        <v>144.0</v>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H150" s="7" t="inlineStr">
+        <is>
+          <t>3500157766</t>
+        </is>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>PHAN THỊ MỸ DUNG</t>
+        </is>
+      </c>
+      <c r="J150" s="6" t="inlineStr">
+        <is>
+          <t>Số 333 Trần Phú, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K150" s="6"/>
+      <c r="L150" s="13" t="n">
+        <v>3425904.0</v>
+      </c>
+      <c r="M150" s="13" t="n">
+        <v>274072.0</v>
+      </c>
+      <c r="N150" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O150" s="13" t="n">
+        <v>3699976.0</v>
+      </c>
+      <c r="P150" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q150" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="n">
+        <v>145.0</v>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H151" s="7"/>
+      <c r="I151" s="6"/>
+      <c r="J151" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K151" s="6"/>
+      <c r="L151" s="13" t="n">
+        <v>1820360.0</v>
+      </c>
+      <c r="M151" s="13" t="n">
+        <v>145629.0</v>
+      </c>
+      <c r="N151" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O151" s="13" t="n">
+        <v>1965989.0</v>
+      </c>
+      <c r="P151" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q151" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="n">
+        <v>146.0</v>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>856</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H152" s="7"/>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>HỒ PHƯỚC KIM BẢO</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="inlineStr">
+        <is>
+          <t>100 Nguyễn Hữu Cảnh Phường Tam Thắng Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K152" s="6"/>
+      <c r="L152" s="13" t="n">
+        <v>4615317.0</v>
+      </c>
+      <c r="M152" s="13" t="n">
+        <v>444680.0</v>
+      </c>
+      <c r="N152" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O152" s="13" t="n">
+        <v>5059997.0</v>
+      </c>
+      <c r="P152" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q152" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="n">
+        <v>147.0</v>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H153" s="7" t="inlineStr">
+        <is>
+          <t>086183017090</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH NGUYỄN THỊ KIM ÁNH</t>
+        </is>
+      </c>
+      <c r="J153" s="6" t="inlineStr">
+        <is>
+          <t>137 đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K153" s="6"/>
+      <c r="L153" s="13" t="n">
+        <v>4227268.0</v>
+      </c>
+      <c r="M153" s="13" t="n">
+        <v>422728.0</v>
+      </c>
+      <c r="N153" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O153" s="13" t="n">
+        <v>4649996.0</v>
+      </c>
+      <c r="P153" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q153" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="n">
+        <v>148.0</v>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H154" s="7"/>
+      <c r="I154" s="6"/>
+      <c r="J154" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K154" s="6"/>
+      <c r="L154" s="13" t="n">
+        <v>8772194.0</v>
+      </c>
+      <c r="M154" s="13" t="n">
+        <v>701775.0</v>
+      </c>
+      <c r="N154" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O154" s="13" t="n">
+        <v>9473969.0</v>
+      </c>
+      <c r="P154" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q154" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="n">
+        <v>149.0</v>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>859</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H155" s="7"/>
+      <c r="I155" s="6"/>
+      <c r="J155" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K155" s="6"/>
+      <c r="L155" s="13" t="n">
+        <v>8741470.0</v>
+      </c>
+      <c r="M155" s="13" t="n">
+        <v>824147.0</v>
+      </c>
+      <c r="N155" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O155" s="13" t="n">
+        <v>9565617.0</v>
+      </c>
+      <c r="P155" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q155" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="n">
+        <v>150.0</v>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H156" s="7"/>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J156" s="6"/>
+      <c r="K156" s="6"/>
+      <c r="L156" s="13" t="n">
+        <v>7113920.0</v>
+      </c>
+      <c r="M156" s="13" t="n">
+        <v>620319.0</v>
+      </c>
+      <c r="N156" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O156" s="13" t="n">
+        <v>7734239.0</v>
+      </c>
+      <c r="P156" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q156" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="n">
+        <v>151.0</v>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D157" s="7" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H157" s="7"/>
+      <c r="I157" s="6"/>
+      <c r="J157" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K157" s="6"/>
+      <c r="L157" s="13" t="n">
+        <v>1.86363E7</v>
+      </c>
+      <c r="M157" s="13" t="n">
+        <v>1863630.0</v>
+      </c>
+      <c r="N157" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O157" s="13" t="n">
+        <v>2.049993E7</v>
+      </c>
+      <c r="P157" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q157" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="n">
+        <v>152.0</v>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H158" s="7"/>
+      <c r="I158" s="6"/>
+      <c r="J158" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K158" s="6"/>
+      <c r="L158" s="13" t="n">
+        <v>3.0E7</v>
+      </c>
+      <c r="M158" s="13" t="n">
+        <v>3000000.0</v>
+      </c>
+      <c r="N158" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O158" s="13" t="n">
+        <v>3.3E7</v>
+      </c>
+      <c r="P158" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q158" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="n">
+        <v>153.0</v>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H159" s="7"/>
+      <c r="I159" s="6"/>
+      <c r="J159" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K159" s="6"/>
+      <c r="L159" s="13" t="n">
+        <v>4.989082E7</v>
+      </c>
+      <c r="M159" s="13" t="n">
+        <v>4989082.0</v>
+      </c>
+      <c r="N159" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O159" s="13" t="n">
+        <v>5.4879902E7</v>
+      </c>
+      <c r="P159" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q159" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="n">
+        <v>154.0</v>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H160" s="7"/>
+      <c r="I160" s="6"/>
+      <c r="J160" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K160" s="6"/>
+      <c r="L160" s="13" t="n">
+        <v>4.5E7</v>
+      </c>
+      <c r="M160" s="13" t="n">
+        <v>4500000.0</v>
+      </c>
+      <c r="N160" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O160" s="13" t="n">
+        <v>4.95E7</v>
+      </c>
+      <c r="P160" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q160" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="n">
+        <v>155.0</v>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H161" s="7"/>
+      <c r="I161" s="6"/>
+      <c r="J161" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K161" s="6"/>
+      <c r="L161" s="13" t="n">
+        <v>6607998.0</v>
+      </c>
+      <c r="M161" s="13" t="n">
+        <v>575913.0</v>
+      </c>
+      <c r="N161" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O161" s="13" t="n">
+        <v>7183911.0</v>
+      </c>
+      <c r="P161" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q161" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="n">
+        <v>156.0</v>
+      </c>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H162" s="7"/>
+      <c r="I162" s="6"/>
+      <c r="J162" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K162" s="6"/>
+      <c r="L162" s="13" t="n">
+        <v>8481600.0</v>
+      </c>
+      <c r="M162" s="13" t="n">
+        <v>793438.0</v>
+      </c>
+      <c r="N162" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O162" s="13" t="n">
+        <v>9275038.0</v>
+      </c>
+      <c r="P162" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q162" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="n">
+        <v>157.0</v>
+      </c>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H163" s="7"/>
+      <c r="I163" s="6"/>
+      <c r="J163" s="6" t="inlineStr">
+        <is>
+          <t>122/29 Lý Tự Trọng Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K163" s="6" t="inlineStr">
+        <is>
+          <t>093083010956</t>
+        </is>
+      </c>
+      <c r="L163" s="13" t="n">
+        <v>1.499092E7</v>
+      </c>
+      <c r="M163" s="13" t="n">
+        <v>1499092.0</v>
+      </c>
+      <c r="N163" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O163" s="13" t="n">
+        <v>1.6490012E7</v>
+      </c>
+      <c r="P163" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q163" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="n">
+        <v>158.0</v>
+      </c>
+      <c r="B164" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H164" s="7"/>
+      <c r="I164" s="6"/>
+      <c r="J164" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K164" s="6"/>
+      <c r="L164" s="13" t="n">
+        <v>8654520.0</v>
+      </c>
+      <c r="M164" s="13" t="n">
+        <v>865452.0</v>
+      </c>
+      <c r="N164" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O164" s="13" t="n">
+        <v>9519972.0</v>
+      </c>
+      <c r="P164" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q164" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="n">
+        <v>159.0</v>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G165" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H165" s="7"/>
+      <c r="I165" s="6"/>
+      <c r="J165" s="6" t="inlineStr">
+        <is>
+          <t>118 Nguyễn Văn Trỗi Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K165" s="6" t="inlineStr">
+        <is>
+          <t>077166000908</t>
+        </is>
+      </c>
+      <c r="L165" s="13" t="n">
+        <v>4572533.0</v>
+      </c>
+      <c r="M165" s="13" t="n">
+        <v>421864.0</v>
+      </c>
+      <c r="N165" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O165" s="13" t="n">
+        <v>4994397.0</v>
+      </c>
+      <c r="P165" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q165" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="n">
+        <v>160.0</v>
+      </c>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H166" s="7"/>
+      <c r="I166" s="6"/>
+      <c r="J166" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K166" s="6"/>
+      <c r="L166" s="13" t="n">
+        <v>6.0487115E7</v>
+      </c>
+      <c r="M166" s="13" t="n">
+        <v>6048712.0</v>
+      </c>
+      <c r="N166" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O166" s="13" t="n">
+        <v>6.6535827E7</v>
+      </c>
+      <c r="P166" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q166" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="n">
+        <v>161.0</v>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H167" s="7" t="inlineStr">
+        <is>
+          <t>077088009229</t>
+        </is>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH TÂM NGUYỄN (DƯƠNG THẾ HUY)</t>
+        </is>
+      </c>
+      <c r="J167" s="6" t="inlineStr">
+        <is>
+          <t>04 đường Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K167" s="6"/>
+      <c r="L167" s="13" t="n">
+        <v>4.7465688E7</v>
+      </c>
+      <c r="M167" s="13" t="n">
+        <v>3797255.0</v>
+      </c>
+      <c r="N167" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O167" s="13" t="n">
+        <v>5.1262943E7</v>
+      </c>
+      <c r="P167" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q167" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="n">
+        <v>162.0</v>
+      </c>
+      <c r="B168" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H168" s="7"/>
+      <c r="I168" s="6"/>
+      <c r="J168" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K168" s="6"/>
+      <c r="L168" s="13" t="n">
+        <v>3276335.0</v>
+      </c>
+      <c r="M168" s="13" t="n">
+        <v>307579.0</v>
+      </c>
+      <c r="N168" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O168" s="13" t="n">
+        <v>3583914.0</v>
+      </c>
+      <c r="P168" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q168" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="n">
+        <v>163.0</v>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H169" s="7"/>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J169" s="6"/>
+      <c r="K169" s="6"/>
+      <c r="L169" s="13" t="n">
+        <v>4046375.0</v>
+      </c>
+      <c r="M169" s="13" t="n">
+        <v>375191.0</v>
+      </c>
+      <c r="N169" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O169" s="13" t="n">
+        <v>4421566.0</v>
+      </c>
+      <c r="P169" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q169" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="n">
+        <v>164.0</v>
+      </c>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G170" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H170" s="7"/>
+      <c r="I170" s="6"/>
+      <c r="J170" s="6" t="inlineStr">
+        <is>
+          <t>57/8 A Nguyễn Hữu  Cảnh, Phường Rạch Dừa Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K170" s="6" t="inlineStr">
+        <is>
+          <t>093185007857</t>
+        </is>
+      </c>
+      <c r="L170" s="13" t="n">
+        <v>3244995.0</v>
+      </c>
+      <c r="M170" s="13" t="n">
+        <v>265055.0</v>
+      </c>
+      <c r="N170" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O170" s="13" t="n">
+        <v>3510050.0</v>
+      </c>
+      <c r="P170" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q170" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="n">
+        <v>165.0</v>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H171" s="7"/>
+      <c r="I171" s="6"/>
+      <c r="J171" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K171" s="6"/>
+      <c r="L171" s="13" t="n">
+        <v>9043920.0</v>
+      </c>
+      <c r="M171" s="13" t="n">
+        <v>866059.0</v>
+      </c>
+      <c r="N171" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O171" s="13" t="n">
+        <v>9909979.0</v>
+      </c>
+      <c r="P171" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q171" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="n">
+        <v>166.0</v>
+      </c>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H172" s="7"/>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J172" s="6"/>
+      <c r="K172" s="6"/>
+      <c r="L172" s="13" t="n">
+        <v>3415775.0</v>
+      </c>
+      <c r="M172" s="13" t="n">
+        <v>273261.0</v>
+      </c>
+      <c r="N172" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O172" s="13" t="n">
+        <v>3689036.0</v>
+      </c>
+      <c r="P172" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q172" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="n">
+        <v>167.0</v>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G173" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H173" s="7"/>
+      <c r="I173" s="6"/>
+      <c r="J173" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K173" s="6"/>
+      <c r="L173" s="13" t="n">
+        <v>8691890.0</v>
+      </c>
+      <c r="M173" s="13" t="n">
+        <v>820856.0</v>
+      </c>
+      <c r="N173" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O173" s="13" t="n">
+        <v>9512746.0</v>
+      </c>
+      <c r="P173" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q173" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="n">
+        <v>168.0</v>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H174" s="7"/>
+      <c r="I174" s="6"/>
+      <c r="J174" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K174" s="6"/>
+      <c r="L174" s="13" t="n">
+        <v>1.096365E7</v>
+      </c>
+      <c r="M174" s="13" t="n">
+        <v>1096365.0</v>
+      </c>
+      <c r="N174" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O174" s="13" t="n">
+        <v>1.2060015E7</v>
+      </c>
+      <c r="P174" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q174" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="n">
+        <v>169.0</v>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G175" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H175" s="7"/>
+      <c r="I175" s="6"/>
+      <c r="J175" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K175" s="6"/>
+      <c r="L175" s="13" t="n">
+        <v>1.2078883E7</v>
+      </c>
+      <c r="M175" s="13" t="n">
+        <v>1108128.0</v>
+      </c>
+      <c r="N175" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O175" s="13" t="n">
+        <v>1.3187011E7</v>
+      </c>
+      <c r="P175" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q175" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="n">
+        <v>170.0</v>
+      </c>
+      <c r="B176" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G176" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H176" s="7"/>
+      <c r="I176" s="6"/>
+      <c r="J176" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K176" s="6"/>
+      <c r="L176" s="13" t="n">
+        <v>3912360.0</v>
+      </c>
+      <c r="M176" s="13" t="n">
+        <v>359015.0</v>
+      </c>
+      <c r="N176" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O176" s="13" t="n">
+        <v>4271375.0</v>
+      </c>
+      <c r="P176" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q176" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="n">
+        <v>171.0</v>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H177" s="7"/>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J177" s="6"/>
+      <c r="K177" s="6"/>
+      <c r="L177" s="13" t="n">
+        <v>7638356.0</v>
+      </c>
+      <c r="M177" s="13" t="n">
+        <v>705614.0</v>
+      </c>
+      <c r="N177" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O177" s="13" t="n">
+        <v>8343970.0</v>
+      </c>
+      <c r="P177" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q177" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="n">
+        <v>172.0</v>
+      </c>
+      <c r="B178" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H178" s="7"/>
+      <c r="I178" s="6"/>
+      <c r="J178" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K178" s="6"/>
+      <c r="L178" s="13" t="n">
+        <v>5112042.0</v>
+      </c>
+      <c r="M178" s="13" t="n">
+        <v>427668.0</v>
+      </c>
+      <c r="N178" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O178" s="13" t="n">
+        <v>5539710.0</v>
+      </c>
+      <c r="P178" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q178" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="n">
+        <v>173.0</v>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>883</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H179" s="7"/>
+      <c r="I179" s="6"/>
+      <c r="J179" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K179" s="6"/>
+      <c r="L179" s="13" t="n">
+        <v>2.25E7</v>
+      </c>
+      <c r="M179" s="13" t="n">
+        <v>2250000.0</v>
+      </c>
+      <c r="N179" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O179" s="13" t="n">
+        <v>2.475E7</v>
+      </c>
+      <c r="P179" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q179" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="n">
+        <v>174.0</v>
+      </c>
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H180" s="7"/>
+      <c r="I180" s="6"/>
+      <c r="J180" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K180" s="6"/>
+      <c r="L180" s="13" t="n">
+        <v>8398510.0</v>
+      </c>
+      <c r="M180" s="13" t="n">
+        <v>791518.0</v>
+      </c>
+      <c r="N180" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O180" s="13" t="n">
+        <v>9190028.0</v>
+      </c>
+      <c r="P180" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q180" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="n">
+        <v>175.0</v>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G181" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H181" s="7"/>
+      <c r="I181" s="6"/>
+      <c r="J181" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K181" s="6"/>
+      <c r="L181" s="13" t="n">
+        <v>1.781818E7</v>
+      </c>
+      <c r="M181" s="13" t="n">
+        <v>1781818.0</v>
+      </c>
+      <c r="N181" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O181" s="13" t="n">
+        <v>1.9599998E7</v>
+      </c>
+      <c r="P181" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q181" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="n">
+        <v>176.0</v>
+      </c>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H182" s="7"/>
+      <c r="I182" s="6"/>
+      <c r="J182" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K182" s="6"/>
+      <c r="L182" s="13" t="n">
+        <v>8666875.0</v>
+      </c>
+      <c r="M182" s="13" t="n">
+        <v>764461.0</v>
+      </c>
+      <c r="N182" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O182" s="13" t="n">
+        <v>9431336.0</v>
+      </c>
+      <c r="P182" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q182" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="n">
+        <v>177.0</v>
+      </c>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F183" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G183" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H183" s="7"/>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>LÊ QUỐC TUẤN</t>
+        </is>
+      </c>
+      <c r="J183" s="6" t="inlineStr">
+        <is>
+          <t>195/6 Hoàng Văn Thụ, Phường Tam Thắng Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K183" s="6"/>
+      <c r="L183" s="13" t="n">
+        <v>2584259.0</v>
+      </c>
+      <c r="M183" s="13" t="n">
+        <v>206741.0</v>
+      </c>
+      <c r="N183" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O183" s="13" t="n">
+        <v>2791000.0</v>
+      </c>
+      <c r="P183" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q183" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="n">
+        <v>178.0</v>
+      </c>
+      <c r="B184" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H184" s="7" t="inlineStr">
+        <is>
+          <t>8498858337</t>
+        </is>
+      </c>
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t>LẠI THỊ ÁNH HỒNG</t>
+        </is>
+      </c>
+      <c r="J184" s="6" t="inlineStr">
+        <is>
+          <t>118 Nguyễn Văn Trỗi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh .</t>
+        </is>
+      </c>
+      <c r="K184" s="6"/>
+      <c r="L184" s="13" t="n">
+        <v>7843955.0</v>
+      </c>
+      <c r="M184" s="13" t="n">
+        <v>728840.0</v>
+      </c>
+      <c r="N184" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O184" s="13" t="n">
+        <v>8572795.0</v>
+      </c>
+      <c r="P184" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q184" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="n">
+        <v>179.0</v>
+      </c>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>889</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H185" s="7"/>
+      <c r="I185" s="6"/>
+      <c r="J185" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K185" s="6"/>
+      <c r="L185" s="13" t="n">
+        <v>4401926.0</v>
+      </c>
+      <c r="M185" s="13" t="n">
+        <v>434175.0</v>
+      </c>
+      <c r="N185" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O185" s="13" t="n">
+        <v>4836101.0</v>
+      </c>
+      <c r="P185" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q185" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n">
+        <v>180.0</v>
+      </c>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H186" s="7"/>
+      <c r="I186" s="6"/>
+      <c r="J186" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K186" s="6"/>
+      <c r="L186" s="13" t="n">
+        <v>7652829.0</v>
+      </c>
+      <c r="M186" s="13" t="n">
+        <v>647136.0</v>
+      </c>
+      <c r="N186" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O186" s="13" t="n">
+        <v>8299965.0</v>
+      </c>
+      <c r="P186" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q186" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>181.0</v>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H187" s="7"/>
+      <c r="I187" s="6"/>
+      <c r="J187" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K187" s="6"/>
+      <c r="L187" s="13" t="n">
+        <v>7794988.0</v>
+      </c>
+      <c r="M187" s="13" t="n">
+        <v>754054.0</v>
+      </c>
+      <c r="N187" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O187" s="13" t="n">
+        <v>8549042.0</v>
+      </c>
+      <c r="P187" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q187" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>182.0</v>
+      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H188" s="7"/>
+      <c r="I188" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J188" s="6"/>
+      <c r="K188" s="6"/>
+      <c r="L188" s="13" t="n">
+        <v>8093660.0</v>
+      </c>
+      <c r="M188" s="13" t="n">
+        <v>745311.0</v>
+      </c>
+      <c r="N188" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O188" s="13" t="n">
+        <v>8838971.0</v>
+      </c>
+      <c r="P188" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q188" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>183.0</v>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H189" s="7"/>
+      <c r="I189" s="6"/>
+      <c r="J189" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K189" s="6"/>
+      <c r="L189" s="13" t="n">
+        <v>2550955.0</v>
+      </c>
+      <c r="M189" s="13" t="n">
+        <v>233299.0</v>
+      </c>
+      <c r="N189" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O189" s="13" t="n">
+        <v>2784254.0</v>
+      </c>
+      <c r="P189" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q189" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>184.0</v>
+      </c>
+      <c r="B190" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H190" s="7"/>
+      <c r="I190" s="6"/>
+      <c r="J190" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K190" s="6"/>
+      <c r="L190" s="13" t="n">
+        <v>1.009089E8</v>
+      </c>
+      <c r="M190" s="13" t="n">
+        <v>1.009089E7</v>
+      </c>
+      <c r="N190" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O190" s="13" t="n">
+        <v>1.1099979E8</v>
+      </c>
+      <c r="P190" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q190" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>185.0</v>
+      </c>
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G191" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H191" s="7"/>
+      <c r="I191" s="6"/>
+      <c r="J191" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K191" s="6"/>
+      <c r="L191" s="13" t="n">
+        <v>7166189.0</v>
+      </c>
+      <c r="M191" s="13" t="n">
+        <v>713619.0</v>
+      </c>
+      <c r="N191" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O191" s="13" t="n">
+        <v>7879808.0</v>
+      </c>
+      <c r="P191" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q191" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="n">
+        <v>186.0</v>
+      </c>
+      <c r="B192" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C192" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H192" s="7"/>
+      <c r="I192" s="6"/>
+      <c r="J192" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K192" s="6"/>
+      <c r="L192" s="13" t="n">
+        <v>4489639.0</v>
+      </c>
+      <c r="M192" s="13" t="n">
+        <v>361352.0</v>
+      </c>
+      <c r="N192" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O192" s="13" t="n">
+        <v>4850991.0</v>
+      </c>
+      <c r="P192" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q192" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="n">
+        <v>187.0</v>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G193" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H193" s="7"/>
+      <c r="I193" s="6"/>
+      <c r="J193" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K193" s="6"/>
+      <c r="L193" s="13" t="n">
+        <v>2.821812E7</v>
+      </c>
+      <c r="M193" s="13" t="n">
+        <v>2821812.0</v>
+      </c>
+      <c r="N193" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O193" s="13" t="n">
+        <v>3.1039932E7</v>
+      </c>
+      <c r="P193" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q193" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="n">
+        <v>188.0</v>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G194" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H194" s="7" t="inlineStr">
+        <is>
+          <t>077080007018</t>
+        </is>
+      </c>
+      <c r="I194" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH CƠM TẤM ĐÊM ANH HUY</t>
+        </is>
+      </c>
+      <c r="J194" s="6" t="inlineStr">
+        <is>
+          <t>Số 179 đường Thống Nhất, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K194" s="6"/>
+      <c r="L194" s="13" t="n">
+        <v>4042455.0</v>
+      </c>
+      <c r="M194" s="13" t="n">
+        <v>323396.0</v>
+      </c>
+      <c r="N194" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O194" s="13" t="n">
+        <v>4365851.0</v>
+      </c>
+      <c r="P194" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q194" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="n">
+        <v>189.0</v>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C195" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D195" s="7" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G195" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H195" s="7"/>
+      <c r="I195" s="6"/>
+      <c r="J195" s="6" t="inlineStr">
+        <is>
+          <t>57/8 A Nguyễn Hữu  Cảnh, Phường Rạch Dừa Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K195" s="6" t="inlineStr">
+        <is>
+          <t>093185007857</t>
+        </is>
+      </c>
+      <c r="L195" s="13" t="n">
+        <v>4868964.0</v>
+      </c>
+      <c r="M195" s="13" t="n">
+        <v>412153.0</v>
+      </c>
+      <c r="N195" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O195" s="13" t="n">
+        <v>5281117.0</v>
+      </c>
+      <c r="P195" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q195" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="n">
+        <v>190.0</v>
+      </c>
+      <c r="B196" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D196" s="7" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="E196" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G196" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H196" s="7"/>
+      <c r="I196" s="6"/>
+      <c r="J196" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K196" s="6"/>
+      <c r="L196" s="13" t="n">
+        <v>3.8164488E7</v>
+      </c>
+      <c r="M196" s="13" t="n">
+        <v>3707705.0</v>
+      </c>
+      <c r="N196" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O196" s="13" t="n">
+        <v>4.1872193E7</v>
+      </c>
+      <c r="P196" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q196" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="n">
+        <v>191.0</v>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D197" s="7" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G197" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H197" s="7" t="inlineStr">
+        <is>
+          <t>034179014597</t>
+        </is>
+      </c>
+      <c r="I197" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH BIDA 89</t>
+        </is>
+      </c>
+      <c r="J197" s="6" t="inlineStr">
+        <is>
+          <t>459/14 TRƯƠNG CÔNG ĐỊNH, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K197" s="6"/>
+      <c r="L197" s="13" t="n">
+        <v>4000045.0</v>
+      </c>
+      <c r="M197" s="13" t="n">
+        <v>367783.0</v>
+      </c>
+      <c r="N197" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O197" s="13" t="n">
+        <v>4367828.0</v>
+      </c>
+      <c r="P197" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q197" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="n">
+        <v>192.0</v>
+      </c>
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D198" s="7" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H198" s="7"/>
+      <c r="I198" s="6"/>
+      <c r="J198" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K198" s="6"/>
+      <c r="L198" s="13" t="n">
+        <v>1.499959E7</v>
+      </c>
+      <c r="M198" s="13" t="n">
+        <v>1272695.0</v>
+      </c>
+      <c r="N198" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O198" s="13" t="n">
+        <v>1.6272285E7</v>
+      </c>
+      <c r="P198" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q198" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="n">
+        <v>193.0</v>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D199" s="7" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="E199" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G199" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H199" s="7"/>
+      <c r="I199" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Ngọc Loan</t>
+        </is>
+      </c>
+      <c r="J199" s="6" t="inlineStr">
+        <is>
+          <t>61/2/1 Nguyễn An Ninh, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K199" s="6" t="inlineStr">
+        <is>
+          <t>077184005373</t>
+        </is>
+      </c>
+      <c r="L199" s="13" t="n">
+        <v>3235201.0</v>
+      </c>
+      <c r="M199" s="13" t="n">
+        <v>258817.0</v>
+      </c>
+      <c r="N199" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O199" s="13" t="n">
+        <v>3494018.0</v>
+      </c>
+      <c r="P199" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q199" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="n">
+        <v>194.0</v>
+      </c>
+      <c r="B200" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D200" s="7" t="inlineStr">
+        <is>
+          <t>904</t>
+        </is>
+      </c>
+      <c r="E200" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G200" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H200" s="7" t="inlineStr">
+        <is>
+          <t>077071003424</t>
+        </is>
+      </c>
+      <c r="I200" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH NGUYỄN MINH HÙNG (QUÁN HÙNG CHI)</t>
+        </is>
+      </c>
+      <c r="J200" s="6" t="inlineStr">
+        <is>
+          <t>F19 Ông Ích Khiêm, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K200" s="6"/>
+      <c r="L200" s="13" t="n">
+        <v>4466592.0</v>
+      </c>
+      <c r="M200" s="13" t="n">
+        <v>357327.0</v>
+      </c>
+      <c r="N200" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O200" s="13" t="n">
+        <v>4823919.0</v>
+      </c>
+      <c r="P200" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q200" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="n">
+        <v>195.0</v>
+      </c>
+      <c r="B201" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>905</t>
+        </is>
+      </c>
+      <c r="E201" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G201" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H201" s="7"/>
+      <c r="I201" s="6"/>
+      <c r="J201" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K201" s="6"/>
+      <c r="L201" s="13" t="n">
+        <v>1.357421E7</v>
+      </c>
+      <c r="M201" s="13" t="n">
+        <v>1176315.0</v>
+      </c>
+      <c r="N201" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O201" s="13" t="n">
+        <v>1.4750525E7</v>
+      </c>
+      <c r="P201" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q201" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="n">
+        <v>196.0</v>
+      </c>
+      <c r="B202" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H202" s="7"/>
+      <c r="I202" s="6"/>
+      <c r="J202" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K202" s="6"/>
+      <c r="L202" s="13" t="n">
+        <v>2.2434952E7</v>
+      </c>
+      <c r="M202" s="13" t="n">
+        <v>2204978.0</v>
+      </c>
+      <c r="N202" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O202" s="13" t="n">
+        <v>2.463993E7</v>
+      </c>
+      <c r="P202" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q202" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="n">
+        <v>197.0</v>
+      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G203" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H203" s="7"/>
+      <c r="I203" s="6"/>
+      <c r="J203" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K203" s="6"/>
+      <c r="L203" s="13" t="n">
+        <v>2.70909E7</v>
+      </c>
+      <c r="M203" s="13" t="n">
+        <v>2709090.0</v>
+      </c>
+      <c r="N203" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O203" s="13" t="n">
+        <v>2.979999E7</v>
+      </c>
+      <c r="P203" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q203" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="n">
+        <v>198.0</v>
+      </c>
+      <c r="B204" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D204" s="7" t="inlineStr">
+        <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G204" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H204" s="7"/>
+      <c r="I204" s="6"/>
+      <c r="J204" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K204" s="6"/>
+      <c r="L204" s="13" t="n">
+        <v>1.151221E7</v>
+      </c>
+      <c r="M204" s="13" t="n">
+        <v>1071684.0</v>
+      </c>
+      <c r="N204" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O204" s="13" t="n">
+        <v>1.2583894E7</v>
+      </c>
+      <c r="P204" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q204" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="n">
+        <v>199.0</v>
+      </c>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G205" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H205" s="7"/>
+      <c r="I205" s="6"/>
+      <c r="J205" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K205" s="6"/>
+      <c r="L205" s="13" t="n">
+        <v>6057214.0</v>
+      </c>
+      <c r="M205" s="13" t="n">
+        <v>558758.0</v>
+      </c>
+      <c r="N205" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O205" s="13" t="n">
+        <v>6615972.0</v>
+      </c>
+      <c r="P205" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q205" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="n">
+        <v>200.0</v>
+      </c>
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G206" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H206" s="7"/>
+      <c r="I206" s="6" t="inlineStr">
+        <is>
+          <t>HỒ PHƯỚC KIM BẢO</t>
+        </is>
+      </c>
+      <c r="J206" s="6" t="inlineStr">
+        <is>
+          <t>100 Nguyễn Hữu Cảnh Phường Tam Thắng Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K206" s="6"/>
+      <c r="L206" s="13" t="n">
+        <v>2.555254E7</v>
+      </c>
+      <c r="M206" s="13" t="n">
+        <v>2527476.0</v>
+      </c>
+      <c r="N206" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O206" s="13" t="n">
+        <v>2.8080016E7</v>
+      </c>
+      <c r="P206" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q206" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="n">
+        <v>201.0</v>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D207" s="7" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G207" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H207" s="7"/>
+      <c r="I207" s="6"/>
+      <c r="J207" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K207" s="6"/>
+      <c r="L207" s="13" t="n">
+        <v>1.5926734E7</v>
+      </c>
+      <c r="M207" s="13" t="n">
+        <v>1513229.0</v>
+      </c>
+      <c r="N207" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O207" s="13" t="n">
+        <v>1.7439963E7</v>
+      </c>
+      <c r="P207" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q207" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="n">
+        <v>202.0</v>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D208" s="7" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G208" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H208" s="7"/>
+      <c r="I208" s="6"/>
+      <c r="J208" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K208" s="6"/>
+      <c r="L208" s="13" t="n">
+        <v>1.1001E7</v>
+      </c>
+      <c r="M208" s="13" t="n">
+        <v>1088989.0</v>
+      </c>
+      <c r="N208" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O208" s="13" t="n">
+        <v>1.2089989E7</v>
+      </c>
+      <c r="P208" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q208" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="n">
+        <v>203.0</v>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>913</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G209" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H209" s="7"/>
+      <c r="I209" s="6"/>
+      <c r="J209" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K209" s="6"/>
+      <c r="L209" s="13" t="n">
+        <v>1.7751685E7</v>
+      </c>
+      <c r="M209" s="13" t="n">
+        <v>1598317.0</v>
+      </c>
+      <c r="N209" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O209" s="13" t="n">
+        <v>1.9350002E7</v>
+      </c>
+      <c r="P209" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q209" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="n">
+        <v>204.0</v>
+      </c>
+      <c r="B210" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D210" s="7" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F210" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G210" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H210" s="7" t="inlineStr">
+        <is>
+          <t>077080007018</t>
+        </is>
+      </c>
+      <c r="I210" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH CƠM TẤM ĐÊM ANH HUY</t>
+        </is>
+      </c>
+      <c r="J210" s="6" t="inlineStr">
+        <is>
+          <t>Số 179 đường Thống Nhất, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K210" s="6"/>
+      <c r="L210" s="13" t="n">
+        <v>4438898.0</v>
+      </c>
+      <c r="M210" s="13" t="n">
+        <v>355111.0</v>
+      </c>
+      <c r="N210" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O210" s="13" t="n">
+        <v>4794009.0</v>
+      </c>
+      <c r="P210" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q210" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="n">
+        <v>205.0</v>
+      </c>
+      <c r="B211" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D211" s="7" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="E211" s="7" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G211" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H211" s="7" t="inlineStr">
+        <is>
+          <t>8498858337</t>
+        </is>
+      </c>
+      <c r="I211" s="6" t="inlineStr">
+        <is>
+          <t>LẠI THỊ ÁNH HỒNG</t>
+        </is>
+      </c>
+      <c r="J211" s="6" t="inlineStr">
+        <is>
+          <t>118 Nguyễn Văn Trỗi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh .</t>
+        </is>
+      </c>
+      <c r="K211" s="6"/>
+      <c r="L211" s="13" t="n">
+        <v>4849924.0</v>
+      </c>
+      <c r="M211" s="13" t="n">
+        <v>387996.0</v>
+      </c>
+      <c r="N211" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O211" s="13" t="n">
+        <v>5237920.0</v>
+      </c>
+      <c r="P211" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q211" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="n">
+        <v>206.0</v>
+      </c>
+      <c r="B212" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D212" s="7" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H212" s="7"/>
+      <c r="I212" s="6"/>
+      <c r="J212" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K212" s="6"/>
+      <c r="L212" s="13" t="n">
+        <v>3.75E7</v>
+      </c>
+      <c r="M212" s="13" t="n">
+        <v>3750000.0</v>
+      </c>
+      <c r="N212" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O212" s="13" t="n">
+        <v>4.125E7</v>
+      </c>
+      <c r="P212" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q212" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="n">
+        <v>207.0</v>
+      </c>
+      <c r="B213" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D213" s="7" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F213" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G213" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H213" s="7"/>
+      <c r="I213" s="6"/>
+      <c r="J213" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K213" s="6"/>
+      <c r="L213" s="13" t="n">
+        <v>2.934546E7</v>
+      </c>
+      <c r="M213" s="13" t="n">
+        <v>2934546.0</v>
+      </c>
+      <c r="N213" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O213" s="13" t="n">
+        <v>3.2280006E7</v>
+      </c>
+      <c r="P213" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q213" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="n">
+        <v>208.0</v>
+      </c>
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D214" s="7" t="inlineStr">
+        <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G214" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H214" s="7"/>
+      <c r="I214" s="6"/>
+      <c r="J214" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K214" s="6"/>
+      <c r="L214" s="13" t="n">
+        <v>1.638052E7</v>
+      </c>
+      <c r="M214" s="13" t="n">
+        <v>1536806.0</v>
+      </c>
+      <c r="N214" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O214" s="13" t="n">
+        <v>1.7917326E7</v>
+      </c>
+      <c r="P214" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q214" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="n">
+        <v>209.0</v>
+      </c>
+      <c r="B215" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D215" s="7" t="inlineStr">
+        <is>
+          <t>919</t>
+        </is>
+      </c>
+      <c r="E215" s="7" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F215" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G215" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H215" s="7"/>
+      <c r="I215" s="6"/>
+      <c r="J215" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K215" s="6"/>
+      <c r="L215" s="13" t="n">
+        <v>1.39545E7</v>
+      </c>
+      <c r="M215" s="13" t="n">
+        <v>1395450.0</v>
+      </c>
+      <c r="N215" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O215" s="13" t="n">
+        <v>1.534995E7</v>
+      </c>
+      <c r="P215" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q215" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="n">
+        <v>210.0</v>
+      </c>
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="E216" s="7" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G216" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H216" s="7"/>
+      <c r="I216" s="6"/>
+      <c r="J216" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K216" s="6"/>
+      <c r="L216" s="13" t="n">
+        <v>4.540915E7</v>
+      </c>
+      <c r="M216" s="13" t="n">
+        <v>4540915.0</v>
+      </c>
+      <c r="N216" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O216" s="13" t="n">
+        <v>4.9950065E7</v>
+      </c>
+      <c r="P216" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q216" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="n">
+        <v>211.0</v>
+      </c>
+      <c r="B217" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D217" s="7" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="E217" s="7" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F217" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G217" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H217" s="7"/>
+      <c r="I217" s="6"/>
+      <c r="J217" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K217" s="6"/>
+      <c r="L217" s="13" t="n">
+        <v>1.50373E7</v>
+      </c>
+      <c r="M217" s="13" t="n">
+        <v>1344466.0</v>
+      </c>
+      <c r="N217" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O217" s="13" t="n">
+        <v>1.6381766E7</v>
+      </c>
+      <c r="P217" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q217" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>
